--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PUJOL MOLLERUSSA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>120.3638</v>
+        <v>116.145</v>
       </c>
       <c r="E2" t="n">
-        <v>89.3794</v>
+        <v>83.25190000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>30.9844</v>
+        <v>32.8931</v>
       </c>
       <c r="G2" t="n">
         <v>68.5027</v>
@@ -610,13 +610,13 @@
         <v>42.4543</v>
       </c>
       <c r="S2" t="n">
-        <v>28.2188</v>
+        <v>24.0001</v>
       </c>
       <c r="T2" t="n">
-        <v>19.8921</v>
+        <v>13.7647</v>
       </c>
       <c r="U2" t="n">
-        <v>8.326700000000001</v>
+        <v>10.2351</v>
       </c>
       <c r="V2" t="n">
         <v>28.007</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>86.09180000000001</v>
+        <v>94.0492</v>
       </c>
       <c r="E3" t="n">
-        <v>60.942</v>
+        <v>66.2869</v>
       </c>
       <c r="F3" t="n">
-        <v>25.1496</v>
+        <v>27.7625</v>
       </c>
       <c r="G3" t="n">
         <v>62.9882</v>
@@ -688,13 +688,13 @@
         <v>41.4624</v>
       </c>
       <c r="S3" t="n">
-        <v>11.2413</v>
+        <v>19.1992</v>
       </c>
       <c r="T3" t="n">
-        <v>5.4608</v>
+        <v>10.8058</v>
       </c>
       <c r="U3" t="n">
-        <v>5.7802</v>
+        <v>8.3932</v>
       </c>
       <c r="V3" t="n">
         <v>9.0847</v>
@@ -721,13 +721,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>59.392</v>
+        <v>68.1549</v>
       </c>
       <c r="E4" t="n">
-        <v>44.4612</v>
+        <v>50.05</v>
       </c>
       <c r="F4" t="n">
-        <v>14.9308</v>
+        <v>18.105</v>
       </c>
       <c r="G4" t="n">
         <v>50.1258</v>
@@ -766,13 +766,13 @@
         <v>37.4947</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6549</v>
+        <v>13.4177</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8352000000000002</v>
+        <v>6.4241</v>
       </c>
       <c r="U4" t="n">
-        <v>3.819500000000001</v>
+        <v>6.9932</v>
       </c>
       <c r="V4" t="n">
         <v>29.0125</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>57.3977</v>
+        <v>63.4882</v>
       </c>
       <c r="E5" t="n">
-        <v>37.049</v>
+        <v>48.9759</v>
       </c>
       <c r="F5" t="n">
-        <v>20.349</v>
+        <v>14.5124</v>
       </c>
       <c r="G5" t="n">
-        <v>27.6088</v>
+        <v>50.5525</v>
       </c>
       <c r="H5" t="n">
-        <v>16.6129</v>
+        <v>12.0302</v>
       </c>
       <c r="I5" t="n">
-        <v>10.9957</v>
+        <v>38.5224</v>
       </c>
       <c r="J5" t="n">
-        <v>30.3248</v>
+        <v>67.3763</v>
       </c>
       <c r="K5" t="n">
-        <v>20.8464</v>
+        <v>25.0989</v>
       </c>
       <c r="L5" t="n">
-        <v>9.478199999999999</v>
+        <v>42.2774</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.716</v>
+        <v>-16.8238</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.2336</v>
+        <v>-13.0686</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5177</v>
+        <v>-3.7553</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7936000000000001</v>
+        <v>2.9761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-32.3363</v>
+        <v>-35.9074</v>
       </c>
       <c r="R5" t="n">
-        <v>31.5431</v>
+        <v>38.8833</v>
       </c>
       <c r="S5" t="n">
-        <v>43.837</v>
+        <v>11.9566</v>
       </c>
       <c r="T5" t="n">
-        <v>29.9077</v>
+        <v>6.9343</v>
       </c>
       <c r="U5" t="n">
-        <v>13.9298</v>
+        <v>5.0225</v>
       </c>
       <c r="V5" t="n">
-        <v>-13.2546</v>
+        <v>-1.9966</v>
       </c>
       <c r="W5" t="n">
-        <v>9.152900000000001</v>
+        <v>10.573</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.4075</v>
+        <v>-12.5698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>53.6461</v>
+        <v>42.5754</v>
       </c>
       <c r="E6" t="n">
-        <v>43.7332</v>
+        <v>25.4267</v>
       </c>
       <c r="F6" t="n">
-        <v>9.912799999999999</v>
+        <v>17.149</v>
       </c>
       <c r="G6" t="n">
-        <v>50.5525</v>
+        <v>14.8219</v>
       </c>
       <c r="H6" t="n">
-        <v>12.0302</v>
+        <v>18.184</v>
       </c>
       <c r="I6" t="n">
-        <v>38.5224</v>
+        <v>-3.3621</v>
       </c>
       <c r="J6" t="n">
-        <v>67.3763</v>
+        <v>31.1483</v>
       </c>
       <c r="K6" t="n">
-        <v>25.0989</v>
+        <v>28.8116</v>
       </c>
       <c r="L6" t="n">
-        <v>42.2774</v>
+        <v>2.336599999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.8238</v>
+        <v>-16.3267</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.0686</v>
+        <v>-10.6276</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.7553</v>
+        <v>-5.699</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9761</v>
+        <v>13.8869</v>
       </c>
       <c r="Q6" t="n">
-        <v>-35.9074</v>
+        <v>-26.3849</v>
       </c>
       <c r="R6" t="n">
-        <v>38.8833</v>
+        <v>40.272</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1142</v>
+        <v>20.3525</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6913</v>
+        <v>11.6726</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4232999999999998</v>
+        <v>8.680199999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.9966</v>
+        <v>-6.4857</v>
       </c>
       <c r="W6" t="n">
-        <v>10.573</v>
+        <v>8.991300000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.5698</v>
+        <v>-15.4771</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>46.127</v>
+        <v>39.682</v>
       </c>
       <c r="E7" t="n">
-        <v>28.2496</v>
+        <v>21.6367</v>
       </c>
       <c r="F7" t="n">
-        <v>17.8773</v>
+        <v>18.0452</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8219</v>
+        <v>27.6088</v>
       </c>
       <c r="H7" t="n">
-        <v>18.184</v>
+        <v>16.6129</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.3621</v>
+        <v>10.9957</v>
       </c>
       <c r="J7" t="n">
-        <v>31.1483</v>
+        <v>30.3248</v>
       </c>
       <c r="K7" t="n">
-        <v>28.8116</v>
+        <v>20.8464</v>
       </c>
       <c r="L7" t="n">
-        <v>2.336599999999999</v>
+        <v>9.478199999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.3267</v>
+        <v>-2.716</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.6276</v>
+        <v>-4.2336</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.699</v>
+        <v>1.5177</v>
       </c>
       <c r="P7" t="n">
-        <v>13.8869</v>
+        <v>-0.7936000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-26.3849</v>
+        <v>-32.3363</v>
       </c>
       <c r="R7" t="n">
-        <v>40.272</v>
+        <v>31.5431</v>
       </c>
       <c r="S7" t="n">
-        <v>23.9039</v>
+        <v>26.1212</v>
       </c>
       <c r="T7" t="n">
-        <v>14.4955</v>
+        <v>14.4956</v>
       </c>
       <c r="U7" t="n">
-        <v>9.4086</v>
+        <v>11.6257</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.4857</v>
+        <v>-13.2546</v>
       </c>
       <c r="W7" t="n">
-        <v>8.991300000000001</v>
+        <v>9.152900000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-15.4771</v>
+        <v>-22.4075</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>26.899</v>
+        <v>22.1019</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7102</v>
+        <v>18.7333</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1889</v>
+        <v>3.3684</v>
       </c>
       <c r="G8" t="n">
         <v>25.3925</v>
@@ -1078,13 +1078,13 @@
         <v>10.3159</v>
       </c>
       <c r="S8" t="n">
-        <v>12.3914</v>
+        <v>7.5939</v>
       </c>
       <c r="T8" t="n">
-        <v>10.4075</v>
+        <v>5.4307</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9837</v>
+        <v>2.1632</v>
       </c>
       <c r="V8" t="n">
         <v>-7.1153</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>8.346499999999999</v>
+        <v>20.518</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.671</v>
+        <v>19.3303</v>
       </c>
       <c r="F9" t="n">
-        <v>9.017100000000001</v>
+        <v>1.1874</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2444</v>
+        <v>13.859</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.139799999999999</v>
+        <v>-2.5536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8954</v>
+        <v>16.4125</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1299</v>
+        <v>25.8712</v>
       </c>
       <c r="K9" t="n">
-        <v>2.763199999999999</v>
+        <v>5.3852</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3668</v>
+        <v>20.4857</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.3743</v>
+        <v>-12.0122</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.9029</v>
+        <v>-7.939</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4717999999999997</v>
+        <v>-4.073399999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>7.7373</v>
+        <v>13.8866</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.6478</v>
+        <v>-14.4818</v>
       </c>
       <c r="R9" t="n">
-        <v>26.3854</v>
+        <v>28.369</v>
       </c>
       <c r="S9" t="n">
-        <v>11.436</v>
+        <v>6.4107</v>
       </c>
       <c r="T9" t="n">
-        <v>5.2784</v>
+        <v>4.2697</v>
       </c>
       <c r="U9" t="n">
-        <v>6.1571</v>
+        <v>2.1412</v>
       </c>
       <c r="V9" t="n">
-        <v>-6.582</v>
+        <v>-13.6384</v>
       </c>
       <c r="W9" t="n">
-        <v>8.5688</v>
+        <v>3.6716</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.1507</v>
+        <v>-17.3101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>6.680900000000001</v>
+        <v>12.031</v>
       </c>
       <c r="E10" t="n">
-        <v>9.9718</v>
+        <v>-6.8391</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.291100000000001</v>
+        <v>18.87</v>
       </c>
       <c r="G10" t="n">
-        <v>13.859</v>
+        <v>-4.739599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5536</v>
+        <v>-5.6032</v>
       </c>
       <c r="I10" t="n">
-        <v>16.4125</v>
+        <v>0.8637000000000007</v>
       </c>
       <c r="J10" t="n">
-        <v>25.8712</v>
+        <v>2.935000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3852</v>
+        <v>-0.03830000000000022</v>
       </c>
       <c r="L10" t="n">
-        <v>20.4857</v>
+        <v>2.9734</v>
       </c>
       <c r="M10" t="n">
-        <v>-12.0122</v>
+        <v>-7.674700000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.939</v>
+        <v>-5.5649</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.073399999999999</v>
+        <v>-2.109399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>13.8866</v>
+        <v>9.324</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.4818</v>
+        <v>-23.4089</v>
       </c>
       <c r="R10" t="n">
-        <v>28.369</v>
+        <v>32.7335</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.4264</v>
+        <v>15.4497</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.0884</v>
+        <v>8.6859</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.3378</v>
+        <v>6.7639</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.6384</v>
+        <v>-8.003500000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6716</v>
+        <v>4.9494</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.3101</v>
+        <v>-12.9528</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>4.1706</v>
+        <v>8.555399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.5847</v>
+        <v>-3.7672</v>
       </c>
       <c r="F11" t="n">
-        <v>17.7552</v>
+        <v>12.3233</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.739599999999999</v>
+        <v>8.1244</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.6032</v>
+        <v>1.0692</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8637000000000007</v>
+        <v>7.055099999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>2.935000000000001</v>
+        <v>20.0971</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03830000000000022</v>
+        <v>12.324</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9734</v>
+        <v>7.7729</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.674700000000001</v>
+        <v>-11.9725</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.5649</v>
+        <v>-11.2549</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.109399999999999</v>
+        <v>-0.7178</v>
       </c>
       <c r="P11" t="n">
-        <v>9.324</v>
+        <v>-3.7691</v>
       </c>
       <c r="Q11" t="n">
-        <v>-23.4089</v>
+        <v>-30.3526</v>
       </c>
       <c r="R11" t="n">
-        <v>32.7335</v>
+        <v>26.5837</v>
       </c>
       <c r="S11" t="n">
-        <v>7.589799999999999</v>
+        <v>9.199299999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9408</v>
+        <v>3.2776</v>
       </c>
       <c r="U11" t="n">
-        <v>5.6492</v>
+        <v>5.9215</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.003500000000001</v>
+        <v>-4.9986</v>
       </c>
       <c r="W11" t="n">
-        <v>4.9494</v>
+        <v>3.211</v>
       </c>
       <c r="X11" t="n">
-        <v>-12.9528</v>
+        <v>-8.2095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7013</v>
+        <v>6.565900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.527</v>
+        <v>-1.351299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1743</v>
+        <v>7.917199999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3279</v>
+        <v>-4.2444</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2463</v>
+        <v>-5.139799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08170000000000011</v>
+        <v>0.8954</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9446</v>
+        <v>4.1299</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6233</v>
+        <v>2.763199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3214</v>
+        <v>1.3668</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6167</v>
+        <v>-8.3743</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3772</v>
+        <v>-7.9029</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2396</v>
+        <v>-0.4717999999999997</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1984</v>
+        <v>7.7373</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9757</v>
+        <v>-18.6478</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1742</v>
+        <v>26.3854</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3218</v>
+        <v>9.6556</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6294000000000001</v>
+        <v>4.5981</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6923999999999999</v>
+        <v>5.0574</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1471</v>
+        <v>-6.582</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.07129999999999997</v>
+        <v>8.5688</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0757</v>
+        <v>-15.1507</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. DOMENGE CABRER</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1816</v>
+        <v>3.3576</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2802</v>
+        <v>2.9351</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0986</v>
+        <v>0.4226</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6097</v>
+        <v>3.3279</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7458</v>
+        <v>3.2463</v>
       </c>
       <c r="I13" t="n">
-        <v>0.136</v>
+        <v>0.08170000000000011</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6802</v>
+        <v>4.9446</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6802</v>
+        <v>4.6233</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.3214</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.6167</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-1.3772</v>
       </c>
       <c r="O13" t="n">
-        <v>0.136</v>
+        <v>-0.2396</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.9757</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.1742</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7913</v>
+        <v>1.9782</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7539</v>
+        <v>1.0375</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0374</v>
+        <v>0.9407</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.1471</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2065</v>
+        <v>-0.07129999999999997</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2065</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="14">
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>J. DOMENGE CABRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.889399999999998</v>
+        <v>-0.1704</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.1419</v>
+        <v>0.872</v>
       </c>
       <c r="F15" t="n">
-        <v>8.2524</v>
+        <v>-1.0425</v>
       </c>
       <c r="G15" t="n">
-        <v>8.1244</v>
+        <v>-0.6097</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0692</v>
+        <v>-0.7458</v>
       </c>
       <c r="I15" t="n">
-        <v>7.055099999999999</v>
+        <v>0.136</v>
       </c>
       <c r="J15" t="n">
-        <v>20.0971</v>
+        <v>-0.6802</v>
       </c>
       <c r="K15" t="n">
-        <v>12.324</v>
+        <v>-0.6802</v>
       </c>
       <c r="L15" t="n">
-        <v>7.7729</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-11.9725</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.2549</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7178</v>
+        <v>0.136</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.7691</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-30.3526</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26.5837</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2457</v>
+        <v>0.4393</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.0967</v>
+        <v>0.3458</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8511</v>
+        <v>0.0935</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.9986</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.211</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.2095</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.0456</v>
+        <v>-6.8902</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0537</v>
+        <v>1.835</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.0991</v>
+        <v>-8.7249</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0965</v>
@@ -1702,13 +1702,13 @@
         <v>12.1015</v>
       </c>
       <c r="S16" t="n">
-        <v>7.3085</v>
+        <v>5.4641</v>
       </c>
       <c r="T16" t="n">
-        <v>4.302899999999999</v>
+        <v>3.0841</v>
       </c>
       <c r="U16" t="n">
-        <v>3.0056</v>
+        <v>2.3798</v>
       </c>
       <c r="V16" t="n">
         <v>-12.2412</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>464.1994</v>
+        <v>490.3000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>318.8973999999999</v>
+        <v>327.3139</v>
       </c>
       <c r="F17" t="n">
-        <v>145.3014</v>
+        <v>162.9871</v>
       </c>
       <c r="G17" t="n">
         <v>313.6135</v>
@@ -1765,7 +1765,7 @@
         <v>-120.0308</v>
       </c>
       <c r="N17" t="n">
-        <v>-98.60899999999997</v>
+        <v>-98.60900000000001</v>
       </c>
       <c r="O17" t="n">
         <v>-21.4223</v>
@@ -1780,13 +1780,13 @@
         <v>371.9714</v>
       </c>
       <c r="S17" t="n">
-        <v>145.0745</v>
+        <v>171.1758</v>
       </c>
       <c r="T17" t="n">
-        <v>86.3481</v>
+        <v>94.76420000000002</v>
       </c>
       <c r="U17" t="n">
-        <v>58.7268</v>
+        <v>76.41110000000002</v>
       </c>
       <c r="V17" t="n">
         <v>-10.3588</v>
